--- a/RC_Catalogo_Questionarios_v1.xlsx
+++ b/RC_Catalogo_Questionarios_v1.xlsx
@@ -4661,8 +4661,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Catalogo" displayName="Catalogo" ref="A3:M199" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A3:M199"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Catalogo" displayName="Catalogo" ref="A3:M200" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A3:M200"/>
   <tableColumns count="13">
     <tableColumn id="1" name="Nº"/>
     <tableColumn id="2" name="Nome do Instrumento"/>
@@ -4861,7 +4861,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M199"/>
+  <dimension ref="A1:M200"/>
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
@@ -13179,6 +13179,66 @@
       </c>
       <c r="M199" s="7" t="s">
         <v>1324</v>
+      </c>
+    </row>
+    <row r="200" customFormat="false" ht="712.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A200" s="5" t="n">
+        <f aca="false">ROW()-3</f>
+        <v>197</v>
+      </c>
+      <c r="B200" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RDP-RC — Registo Diário Prospetivo</t>
+        </is>
+      </c>
+      <c r="C200" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Regulação Emocional &amp; Coping</t>
+        </is>
+      </c>
+      <c r="D200" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Próprio</t>
+        </is>
+      </c>
+      <c r="E200" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12–99 anos</t>
+        </is>
+      </c>
+      <c r="F200" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="G200" s="5" t="n">
+        <v>99</v>
+      </c>
+      <c r="H200" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="I200" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Regista PROSPETIVAMENTE, dia a dia, a variação sintomática ao longo do ciclo menstrual, para testar se o agravamento se concentra na FASE LÚTEA TARDIA. Instrumento de CONSTRUÇÃO PRÓPRIA, em português europeu, SEM validação psicométrica, sem normas e sem estudo de fidelidade: é um dispositivo de OBSERVAÇÃO ESTRUTURADA, não um teste. Cada registo diário cobre 11 itens de critério numa escala 0–3 (0 nada · 1 um pouco · 2 bastante · 3 muito) — 4 NUCLEARES (labilidade do humor, irritabilidade, humor deprimido, ansiedade) e 7 ADICIONAIS (interesse, concentração, fadiga, apetite, sono, sobrecarga, sintomas físicos) —, devolvendo um Total de critério 0–33, mais um item de INTERFERÊNCIA no dia (0–3) e dois sinalizadores binários (dia de fluxo menstrual; toma de medicação em SOS). Corre ainda, EM PARALELO, um bloco de três sintomas específicos do caso (sintomas digestivos, cefaleia, acordar sem descanso) e as horas de sono — que NÃO entram no Total de critério nem em qualquer critério do DSM-5-TR e servem apenas de leitura ecológica acompanhante. ⚠ A FASE NÃO É CALCULADA A PARTIR DO INÍCIO DO CICLO: em ciclos de 35–40 dias a fase lútea não é contável para a frente, pelo que é atribuída RETROSPETIVAMENTE a partir do início da menstruação SEGUINTE — lútea tardia = os 7 dias anteriores ao início do fluxo; folicular = dias 3 a 9 após o início do fluxo; os restantes ficam intermédios e não entram na comparação. Por isso a classificação de um dia pode mudar quando chega o ciclo seguinte, e só estabiliza no fim. ⚠ O DSM-5-TR exige DOIS ciclos prospetivos completos: abaixo disso o padrão devolvido é R0 e nenhuma leitura substantiva é admissível. ⚠ A leitura primária é o CONTRASTE lútea vs folicular, nunca o valor absoluto de um dia: considera-se agravamento assinalável uma variação ≥ 30% da média lútea sobre a média folicular, e um item conta como presente quando atinge 2 ou mais em pelo menos metade dos dias lúteos. ⚠ A DISSOCIAÇÃO entre PMDD e exacerbação pré-menstrual (PME) faz-se pelo NÍVEL BASAL folicular: com média por item ≥ 1,0 na fase folicular, o quadro é de agravamento de sintomatologia já presente, e o DSM-5-TR EXCLUI o diagnóstico de PMDD — a implicação clínica é tratar o quadro de base, com atenção acrescida na janela lútea. Padrões devolvidos: R0 registo insuficiente · R1 sem agravamento assinalável · R2 exacerbação pré-menstrual de quadro preexistente · R3 compatível com PMDD · R4 agravamento lúteo subclínico. ⚠ R3 é uma COMPATIBILIDADE DE PADRÃO, nunca um diagnóstico: a confirmação diagnóstica e a decisão terapêutica são da PSIQUIATRIA. ⚠ Ausência de agravamento cíclico (R1) é informação clínica de pleno direito: exclui o ciclo como fator de manutenção e remete a procura para outro eixo. ⚠ Registo DIÁRIO — uma linha por dia e por utente, não um protocolo único; a adesão ao registo é ela própria dado clínico, e falhas sistemáticas numa das fases enviesam a comparação</t>
+        </is>
+      </c>
+      <c r="J200" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Total de critério (11 itens, 0–33) — soma dos 4 nucleares com os 7 adicionais; é a pontuação que entra na comparação entre fases | Sintomas nucleares (4 itens, 0–12) — labilidade do humor, irritabilidade, humor deprimido e ansiedade; o DSM-5-TR exige pelo menos UM presente | Sintomas adicionais (7 itens, 0–21) — interesse, concentração, fadiga, apetite, sono, sobrecarga e sintomas físicos | Interferência no dia (1 item, 0–3) — impacto declarado no funcionamento desse dia, seguido em paralelo às médias de fase | Bloco específico do caso (sintomas digestivos, cefaleia, acordar sem descanso) — corre EM PARALELO e NÃO entra no Total de critério nem em qualquer critério do DSM-5-TR | Horas de sono declaradas — indicador ecológico externo a qualquer pontuação; média comparada entre fases | Sinalizador de fluxo menstrual (0/1) — não é sintoma: é o marcador que delimita retrospetivamente as fases | Sinalizador de medicação em SOS (0/1) — proporção de dias com recurso a SOS, comparada entre fases | Atribuição RETROSPETIVA de fase — lútea tardia (7 dias anteriores ao início do fluxo) · folicular (dias 3 a 9 após o início do fluxo) · intermédia (excluída da comparação); a classificação de um dia só estabiliza quando chega o ciclo seguinte | Médias por fase — média do Total de critério nos dias lúteos e nos dias foliculares, com o número de dias efetivamente disponíveis em cada uma | Variação lútea-folicular (%) — agravamento assinalável a partir de 30%; com média folicular inferior a 1,0 a variação é truncada em 200% e lida como remissão folicular | Itens presentes em pelo menos metade dos dias lúteos — item conta como presente a partir de 2; critério de contagem sintomática (≥ 5 itens, com ≥ 1 nuclear) | Nível basal folicular (média por item) — discriminante entre PMDD e exacerbação pré-menstrual: a partir de 1,0 o DSM-5-TR exclui PMDD por se tratar de agravamento de quadro preexistente | Padrão devolvido — R0 registo insuficiente (menos de dois ciclos completos) · R1 sem agravamento assinalável · R2 exacerbação pré-menstrual (PME) · R3 compatível com PMDD · R4 agravamento lúteo subclínico; R3 é compatibilidade de padrão, nunca diagnóstico | Número de ciclos prospetivos completos — o DSM-5-TR exige DOIS; abaixo disso nenhuma leitura substantiva é admissível</t>
+        </is>
+      </c>
+      <c r="K200" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rdp_rc</t>
+        </is>
+      </c>
+      <c r="L200" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">q_rdp_rc</t>
+        </is>
+      </c>
+      <c r="M200" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://correiaricardina-ui.github.io/questionarios/RDP_RC_v1.html</t>
+        </is>
       </c>
     </row>
   </sheetData>
